--- a/data/Health_sector_companies.xlsx
+++ b/data/Health_sector_companies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/moham09/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/moham09/Downloads/job-search-agent/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{312C21FA-E87C-8E4A-A58D-66BCC320A877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26909B9E-A538-AF46-90D7-08E07D5A6CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{4BC829A6-0186-C14E-90CB-4600834BEDB2}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{4BC829A6-0186-C14E-90CB-4600834BEDB2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>#</t>
   </si>
@@ -110,6 +110,24 @@
   </si>
   <si>
     <t>https://jobs.lever.co/aledade</t>
+  </si>
+  <si>
+    <t>Globus Medical</t>
+  </si>
+  <si>
+    <t>https://globusmedical.wd5.myworkdayjobs.com/en-US/GMED_Careers</t>
+  </si>
+  <si>
+    <t>GE HealthCare</t>
+  </si>
+  <si>
+    <t>https://gehc.wd5.myworkdayjobs.com/GEHC_ExternalSite</t>
+  </si>
+  <si>
+    <t>Omnicell</t>
+  </si>
+  <si>
+    <t>https://apply.omnicell.com/careers/</t>
   </si>
 </sst>
 </file>
@@ -181,12 +199,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -502,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21BC077-D33A-BA47-BE41-79152B5F9F54}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.33203125" customWidth="1"/>
@@ -522,7 +543,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -533,7 +554,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -544,7 +565,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -555,7 +576,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" t="s">
@@ -566,7 +587,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" t="s">
@@ -577,7 +598,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" t="s">
@@ -588,7 +609,7 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" t="s">
@@ -599,7 +620,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" t="s">
@@ -610,7 +631,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" t="s">
@@ -621,7 +642,7 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
       <c r="B11" t="s">
@@ -632,7 +653,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
       <c r="B12" t="s">
@@ -640,6 +661,39 @@
       </c>
       <c r="C12" s="2" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -655,6 +709,9 @@
     <hyperlink ref="C10" r:id="rId9" xr:uid="{7CE41C9D-54AA-B748-AC9A-4EF1C31CC9B6}"/>
     <hyperlink ref="C11" r:id="rId10" xr:uid="{4181165B-EE2E-9E43-8A54-F14FF0370239}"/>
     <hyperlink ref="C12" r:id="rId11" xr:uid="{9426D8AB-A388-0443-B433-9D20D1569C79}"/>
+    <hyperlink ref="C13" r:id="rId12" xr:uid="{79839241-616E-CB4E-B889-34419BC9381E}"/>
+    <hyperlink ref="C14" r:id="rId13" xr:uid="{51D79506-9760-224B-8544-AAE9E02BADC4}"/>
+    <hyperlink ref="C15" r:id="rId14" xr:uid="{A411454C-FF35-5E45-AF86-F93D11A9E922}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Health_sector_companies.xlsx
+++ b/data/Health_sector_companies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/moham09/Downloads/job-search-agent/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26909B9E-A538-AF46-90D7-08E07D5A6CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D9716E-E173-1343-999F-EE286B1E5C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{4BC829A6-0186-C14E-90CB-4600834BEDB2}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>#</t>
   </si>
@@ -128,6 +128,36 @@
   </si>
   <si>
     <t>https://apply.omnicell.com/careers/</t>
+  </si>
+  <si>
+    <t>https://onehealthineers.wd3.myworkdayjobs.com/SHSJB</t>
+  </si>
+  <si>
+    <t>Siemens Healthineers</t>
+  </si>
+  <si>
+    <t>https://bdx.wd1.myworkdayjobs.com/EXTERNAL_CAREER_SITE_USA</t>
+  </si>
+  <si>
+    <t>BD</t>
+  </si>
+  <si>
+    <t>https://humana.wd5.myworkdayjobs.com/Humana_External_Career_Site</t>
+  </si>
+  <si>
+    <t>Humana</t>
+  </si>
+  <si>
+    <t>https://uhg.taleo.net/careersection/10030/joblist.ftl</t>
+  </si>
+  <si>
+    <t>Optum</t>
+  </si>
+  <si>
+    <t>CVS Health</t>
+  </si>
+  <si>
+    <t>https://cvshealth.wd1.myworkdayjobs.com/en-US/CVS_Health_Careers/jobs</t>
   </si>
 </sst>
 </file>
@@ -523,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21BC077-D33A-BA47-BE41-79152B5F9F54}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.33203125" customWidth="1"/>
@@ -694,6 +724,61 @@
       </c>
       <c r="C15" s="2" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -712,6 +797,11 @@
     <hyperlink ref="C13" r:id="rId12" xr:uid="{79839241-616E-CB4E-B889-34419BC9381E}"/>
     <hyperlink ref="C14" r:id="rId13" xr:uid="{51D79506-9760-224B-8544-AAE9E02BADC4}"/>
     <hyperlink ref="C15" r:id="rId14" xr:uid="{A411454C-FF35-5E45-AF86-F93D11A9E922}"/>
+    <hyperlink ref="C16" r:id="rId15" xr:uid="{7CDDE387-292F-1847-8141-688D03B7EE7B}"/>
+    <hyperlink ref="C17" r:id="rId16" xr:uid="{6551E627-E596-784D-99DE-BBE320CC4503}"/>
+    <hyperlink ref="C18" r:id="rId17" xr:uid="{0213187C-772B-864C-A3EF-BCB3A4B62DA7}"/>
+    <hyperlink ref="C19" r:id="rId18" xr:uid="{1E27AC32-E971-DF47-A2F3-76D1C10B7BC5}"/>
+    <hyperlink ref="C20" r:id="rId19" xr:uid="{F464DE66-540B-804C-A270-CB5E8AAD55C8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Health_sector_companies.xlsx
+++ b/data/Health_sector_companies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/moham09/Downloads/job-search-agent/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D9716E-E173-1343-999F-EE286B1E5C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8227ACC-0D4D-0E4E-88F0-7814B0A4AB18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{4BC829A6-0186-C14E-90CB-4600834BEDB2}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>#</t>
   </si>
@@ -158,6 +158,72 @@
   </si>
   <si>
     <t>https://cvshealth.wd1.myworkdayjobs.com/en-US/CVS_Health_Careers/jobs</t>
+  </si>
+  <si>
+    <t>The Cigna Group</t>
+  </si>
+  <si>
+    <t>https://jobs.thecignagroup.com/us/en/search-results</t>
+  </si>
+  <si>
+    <t>Centene Corporation</t>
+  </si>
+  <si>
+    <t>https://centene.wd5.myworkdayjobs.com/Centene_External</t>
+  </si>
+  <si>
+    <t>Elevance Health</t>
+  </si>
+  <si>
+    <t>https://elevancehealth.wd1.myworkdayjobs.com/en-US/ANT</t>
+  </si>
+  <si>
+    <t>Molina</t>
+  </si>
+  <si>
+    <t>https://apply.molinahealthcare.com/hcmUI/CandidateExperience/en/sites/CX_1/jobs</t>
+  </si>
+  <si>
+    <t>Cardinal Health</t>
+  </si>
+  <si>
+    <t>https://cardinalhealth.wd1.myworkdayjobs.com/en-US/EXT</t>
+  </si>
+  <si>
+    <t>McKesson</t>
+  </si>
+  <si>
+    <t>https://mckesson.wd3.myworkdayjobs.com/en-US/External_Careers</t>
+  </si>
+  <si>
+    <t>Abbot</t>
+  </si>
+  <si>
+    <t>https://www.jobs.abbott/us/en/search-results</t>
+  </si>
+  <si>
+    <t>Boston Scientific</t>
+  </si>
+  <si>
+    <t>https://bostonscientific.eightfold.ai/careers/</t>
+  </si>
+  <si>
+    <t>Philips</t>
+  </si>
+  <si>
+    <t>https://philips.wd3.myworkdayjobs.com/en-US/jobs-and-careers</t>
+  </si>
+  <si>
+    <t>Pfizer</t>
+  </si>
+  <si>
+    <t>https://pfizer.wd1.myworkdayjobs.com/en-US/PfizerCareers/</t>
+  </si>
+  <si>
+    <t>Novartis</t>
+  </si>
+  <si>
+    <t>https://novartis.wd3.myworkdayjobs.com/en-US/Novartis_Careers</t>
   </si>
 </sst>
 </file>
@@ -553,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21BC077-D33A-BA47-BE41-79152B5F9F54}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.33203125" customWidth="1"/>
@@ -779,6 +845,127 @@
       </c>
       <c r="C20" s="2" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -802,6 +989,17 @@
     <hyperlink ref="C18" r:id="rId17" xr:uid="{0213187C-772B-864C-A3EF-BCB3A4B62DA7}"/>
     <hyperlink ref="C19" r:id="rId18" xr:uid="{1E27AC32-E971-DF47-A2F3-76D1C10B7BC5}"/>
     <hyperlink ref="C20" r:id="rId19" xr:uid="{F464DE66-540B-804C-A270-CB5E8AAD55C8}"/>
+    <hyperlink ref="C21" r:id="rId20" xr:uid="{98728E07-7789-2448-9F6D-2AC626460F6A}"/>
+    <hyperlink ref="C22" r:id="rId21" xr:uid="{396D9EBC-A6B4-3843-BB23-E5663A4FD795}"/>
+    <hyperlink ref="C23" r:id="rId22" xr:uid="{A61B9FC4-91A6-1644-941B-063A6B5EC472}"/>
+    <hyperlink ref="C24" r:id="rId23" xr:uid="{2E706783-3883-DA48-905E-A7772504FECA}"/>
+    <hyperlink ref="C25" r:id="rId24" xr:uid="{462F04B8-226A-9A41-A103-217CA5383186}"/>
+    <hyperlink ref="C26" r:id="rId25" xr:uid="{8D6DEF06-E5D8-1843-AB3D-9E48240B40A4}"/>
+    <hyperlink ref="C27" r:id="rId26" xr:uid="{091F94E3-FB95-9140-A261-84B01493549E}"/>
+    <hyperlink ref="C28" r:id="rId27" xr:uid="{B768D8EF-289C-EF42-80B3-EE5786FFBDD7}"/>
+    <hyperlink ref="C29" r:id="rId28" xr:uid="{B220A759-2FFA-EC4F-B1C6-373715D32390}"/>
+    <hyperlink ref="C30" r:id="rId29" xr:uid="{425FF688-E3FB-A54D-B95C-F86EBA46C11A}"/>
+    <hyperlink ref="C31" r:id="rId30" xr:uid="{080A73F6-AC68-0C49-A61A-8270F11111B3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Health_sector_companies.xlsx
+++ b/data/Health_sector_companies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/moham09/Downloads/job-search-agent/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8227ACC-0D4D-0E4E-88F0-7814B0A4AB18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1559C2F-6331-0440-9DC7-D667CF9BE6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{4BC829A6-0186-C14E-90CB-4600834BEDB2}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>#</t>
   </si>
@@ -224,6 +224,30 @@
   </si>
   <si>
     <t>https://novartis.wd3.myworkdayjobs.com/en-US/Novartis_Careers</t>
+  </si>
+  <si>
+    <t>Sanofi</t>
+  </si>
+  <si>
+    <t>https://jobs.sanofi.com/en/search-jobs/</t>
+  </si>
+  <si>
+    <t>GSK</t>
+  </si>
+  <si>
+    <t>https://gsk.wd5.myworkdayjobs.com/GSKCareers/</t>
+  </si>
+  <si>
+    <t>Astrazeneca</t>
+  </si>
+  <si>
+    <t>https://astrazeneca.eightfold.ai/careers/</t>
+  </si>
+  <si>
+    <t>P&amp;G</t>
+  </si>
+  <si>
+    <t>https://www.pgcareers.com/global/en/search-results</t>
   </si>
 </sst>
 </file>
@@ -619,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21BC077-D33A-BA47-BE41-79152B5F9F54}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.33203125" customWidth="1"/>
@@ -966,6 +990,50 @@
       </c>
       <c r="C31" s="2" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="3">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="3">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1000,6 +1068,10 @@
     <hyperlink ref="C29" r:id="rId28" xr:uid="{B220A759-2FFA-EC4F-B1C6-373715D32390}"/>
     <hyperlink ref="C30" r:id="rId29" xr:uid="{425FF688-E3FB-A54D-B95C-F86EBA46C11A}"/>
     <hyperlink ref="C31" r:id="rId30" xr:uid="{080A73F6-AC68-0C49-A61A-8270F11111B3}"/>
+    <hyperlink ref="C32" r:id="rId31" xr:uid="{0EEA40BB-29F9-5D44-B6EB-1406D0A716AF}"/>
+    <hyperlink ref="C33" r:id="rId32" xr:uid="{EFA25233-17DE-9C4B-9029-0FC2BFDB9524}"/>
+    <hyperlink ref="C34" r:id="rId33" xr:uid="{3018D7A7-2AA9-FD4F-B0BA-77BC9DF1F738}"/>
+    <hyperlink ref="C35" r:id="rId34" xr:uid="{4B64B7D8-98D9-884A-93BD-277B9B36CCAB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
